--- a/artfynd/A 31314-2023 artfynd.xlsx
+++ b/artfynd/A 31314-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126239315</v>
       </c>
       <c r="B2" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126239314</v>
       </c>
       <c r="B3" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31314-2023 artfynd.xlsx
+++ b/artfynd/A 31314-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126239315</v>
       </c>
       <c r="B2" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126239314</v>
       </c>
       <c r="B3" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31314-2023 artfynd.xlsx
+++ b/artfynd/A 31314-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126239315</v>
       </c>
       <c r="B2" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126239314</v>
       </c>
       <c r="B3" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31314-2023 artfynd.xlsx
+++ b/artfynd/A 31314-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126239315</v>
       </c>
       <c r="B2" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126239314</v>
       </c>
       <c r="B3" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31314-2023 artfynd.xlsx
+++ b/artfynd/A 31314-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126239315</v>
+        <v>101900326</v>
       </c>
       <c r="B2" t="n">
-        <v>100543</v>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ebbegärde med omnejd, Sm</t>
+          <t>S Lassakärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573038</v>
+        <v>572980</v>
       </c>
       <c r="R2" t="n">
-        <v>6300116</v>
+        <v>6300139</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +778,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +793,7 @@
         <v>126239314</v>
       </c>
       <c r="B3" t="n">
-        <v>105396</v>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -871,6 +884,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126239315</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ebbegärde med omnejd, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573038</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6300116</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31314-2023 artfynd.xlsx
+++ b/artfynd/A 31314-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101900326</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126239314</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,8 +1001,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126239315</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>